--- a/tests/Browser/Excel/TaiLieuBieuQuyet.xlsx
+++ b/tests/Browser/Excel/TaiLieuBieuQuyet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\TuDongLamViec\tests\Browser\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D659F18-C0D4-4E27-9EA5-48EEED11F6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6E15CB-411E-4EA1-9239-CA3E0B84503F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="2490" windowWidth="19200" windowHeight="10060" xr2:uid="{06A80A3C-E8BE-424B-9614-FA41F15A8077}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{06A80A3C-E8BE-424B-9614-FA41F15A8077}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
   <si>
     <t>ten_cuoc_hop</t>
   </si>
@@ -81,106 +81,52 @@
     <t>NQ-010</t>
   </si>
   <si>
-    <t>Cuộc họp A (24/8/2026)</t>
-  </si>
-  <si>
-    <t>NQ-011</t>
-  </si>
-  <si>
-    <t>NQ-012</t>
-  </si>
-  <si>
-    <t>NQ-013</t>
-  </si>
-  <si>
-    <t>NQ-014</t>
-  </si>
-  <si>
-    <t>NQ-015</t>
-  </si>
-  <si>
-    <t>NQ-016</t>
-  </si>
-  <si>
-    <t>NQ-017</t>
-  </si>
-  <si>
-    <t>NQ-018</t>
-  </si>
-  <si>
-    <t>NQ-019</t>
-  </si>
-  <si>
-    <t>NQ-020</t>
-  </si>
-  <si>
-    <t>NQ-021</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 1</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 2</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 3</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 4</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 5</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 6</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 7</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 8</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 9</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 10</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 11</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 12</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 13</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 14</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 15</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 16</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 17</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 18</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 19</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 20</t>
-  </si>
-  <si>
-    <t>Biểu quyết 10/9 số 21</t>
-  </si>
-  <si>
     <t>TỜ TRÌNH.pdf</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 1</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 2</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 3</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 4</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 5</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 6</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 7</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 8</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 9</t>
+  </si>
+  <si>
+    <t>Biểu quyết số 10</t>
+  </si>
+  <si>
+    <t>chu_tri_bieu_quyet</t>
+  </si>
+  <si>
+    <t>Cuộc họp tỉnh giả định (21/09/2026)</t>
+  </si>
+  <si>
+    <t>Chủ trì tỉnh 2</t>
+  </si>
+  <si>
+    <t>Chủ trì tỉnh 3</t>
+  </si>
+  <si>
+    <t>Chủ trì tỉnh</t>
   </si>
 </sst>
 </file>
@@ -561,14 +507,14 @@
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.6328125" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="15.453125" customWidth="1"/>
     <col min="4" max="4" width="18.453125" customWidth="1"/>
     <col min="5" max="5" width="16.6328125" customWidth="1"/>
     <col min="6" max="6" width="31.08984375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.08984375" customWidth="1"/>
+    <col min="8" max="8" width="21.26953125" customWidth="1"/>
     <col min="9" max="9" width="12.453125" customWidth="1"/>
     <col min="10" max="10" width="10.36328125" customWidth="1"/>
     <col min="11" max="11" width="15.81640625" customWidth="1"/>
@@ -596,7 +542,9 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -604,7 +552,7 @@
     </row>
     <row r="2" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
@@ -614,15 +562,17 @@
         <v>46262</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -630,7 +580,7 @@
     </row>
     <row r="3" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
@@ -640,15 +590,17 @@
         <v>46262</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -656,7 +608,7 @@
     </row>
     <row r="4" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="2" t="s">
@@ -666,15 +618,17 @@
         <v>46262</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -682,7 +636,7 @@
     </row>
     <row r="5" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2" t="s">
@@ -692,15 +646,17 @@
         <v>46262</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -708,7 +664,7 @@
     </row>
     <row r="6" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="2" t="s">
@@ -718,15 +674,17 @@
         <v>46262</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -734,7 +692,7 @@
     </row>
     <row r="7" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="2" t="s">
@@ -744,15 +702,17 @@
         <v>46262</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -760,7 +720,7 @@
     </row>
     <row r="8" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="2" t="s">
@@ -770,15 +730,17 @@
         <v>46262</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -786,7 +748,7 @@
     </row>
     <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="2" t="s">
@@ -796,15 +758,17 @@
         <v>46262</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -812,7 +776,7 @@
     </row>
     <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="2" t="s">
@@ -822,15 +786,17 @@
         <v>46262</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -838,7 +804,7 @@
     </row>
     <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="2" t="s">
@@ -848,13 +814,13 @@
         <v>46262</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -862,225 +828,93 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="3">
-        <v>46262</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>51</v>
-      </c>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
